--- a/data/base/Backlog_44.xlsx
+++ b/data/base/Backlog_44.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19595F3B-1312-44F4-AB98-997DAC166CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA681F10-B78C-48EB-9FA6-169D91E0B7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -103,9 +103,6 @@
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Felipe Nascimento</t>
   </si>
   <si>
@@ -131,6 +128,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Erick da Silva</t>
   </si>
 </sst>
 </file>
@@ -654,7 +654,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -669,16 +669,16 @@
         <v>45968</v>
       </c>
       <c r="G2" s="9">
-        <v>4865</v>
+        <v>4792</v>
       </c>
       <c r="H2" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I2" s="2">
         <v>45964</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>14</v>
@@ -689,7 +689,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -704,16 +704,16 @@
         <v>45968</v>
       </c>
       <c r="G3" s="9">
-        <v>4849</v>
+        <v>4677</v>
       </c>
       <c r="H3" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I3" s="2">
         <v>45964</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>14</v>
@@ -724,7 +724,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -739,16 +739,16 @@
         <v>45968</v>
       </c>
       <c r="G4" s="9">
-        <v>4848</v>
+        <v>4134</v>
       </c>
       <c r="H4" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I4" s="2">
         <v>45964</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>14</v>
@@ -759,7 +759,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -774,10 +774,10 @@
         <v>45968</v>
       </c>
       <c r="G5" s="9">
-        <v>4844</v>
+        <v>3264</v>
       </c>
       <c r="H5" s="3">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="I5" s="2">
         <v>45964</v>
@@ -794,7 +794,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -809,16 +809,16 @@
         <v>45968</v>
       </c>
       <c r="G6" s="9">
-        <v>4837</v>
+        <v>4679</v>
       </c>
       <c r="H6" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I6" s="2">
         <v>45964</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>14</v>
@@ -829,7 +829,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -844,7 +844,7 @@
         <v>45968</v>
       </c>
       <c r="G7" s="9">
-        <v>4836</v>
+        <v>4844</v>
       </c>
       <c r="H7" s="3">
         <v>45962</v>
@@ -864,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -879,7 +879,7 @@
         <v>45968</v>
       </c>
       <c r="G8" s="9">
-        <v>4831</v>
+        <v>4837</v>
       </c>
       <c r="H8" s="3">
         <v>45962</v>
@@ -899,7 +899,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
@@ -914,7 +914,7 @@
         <v>45968</v>
       </c>
       <c r="G9" s="9">
-        <v>4814</v>
+        <v>4836</v>
       </c>
       <c r="H9" s="3">
         <v>45962</v>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
@@ -949,16 +949,16 @@
         <v>45968</v>
       </c>
       <c r="G10" s="9">
-        <v>4792</v>
+        <v>4831</v>
       </c>
       <c r="H10" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I10" s="2">
         <v>45964</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>14</v>
@@ -969,7 +969,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -984,16 +984,16 @@
         <v>45968</v>
       </c>
       <c r="G11" s="9">
-        <v>4745</v>
+        <v>4814</v>
       </c>
       <c r="H11" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I11" s="2">
         <v>45964</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>14</v>
@@ -1004,7 +1004,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -1039,7 +1039,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1054,7 +1054,7 @@
         <v>45968</v>
       </c>
       <c r="G13" s="9">
-        <v>4679</v>
+        <v>4605</v>
       </c>
       <c r="H13" s="3">
         <v>45931</v>
@@ -1063,7 +1063,7 @@
         <v>45964</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>14</v>
@@ -1074,7 +1074,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1089,7 +1089,7 @@
         <v>45968</v>
       </c>
       <c r="G14" s="9">
-        <v>4677</v>
+        <v>4326</v>
       </c>
       <c r="H14" s="3">
         <v>45931</v>
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1124,16 +1124,16 @@
         <v>45968</v>
       </c>
       <c r="G15" s="9">
-        <v>4656</v>
+        <v>4319</v>
       </c>
       <c r="H15" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I15" s="2">
         <v>45964</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>14</v>
@@ -1144,7 +1144,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1159,16 +1159,16 @@
         <v>45968</v>
       </c>
       <c r="G16" s="9">
-        <v>4636</v>
+        <v>4656</v>
       </c>
       <c r="H16" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I16" s="2">
         <v>45964</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>14</v>
@@ -1179,7 +1179,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
@@ -1194,7 +1194,7 @@
         <v>45968</v>
       </c>
       <c r="G17" s="9">
-        <v>4605</v>
+        <v>4445</v>
       </c>
       <c r="H17" s="3">
         <v>45931</v>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
@@ -1229,7 +1229,7 @@
         <v>45968</v>
       </c>
       <c r="G18" s="9">
-        <v>4578</v>
+        <v>4365</v>
       </c>
       <c r="H18" s="3">
         <v>45931</v>
@@ -1249,7 +1249,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1264,7 +1264,7 @@
         <v>45968</v>
       </c>
       <c r="G19" s="9">
-        <v>4527</v>
+        <v>4361</v>
       </c>
       <c r="H19" s="3">
         <v>45931</v>
@@ -1284,7 +1284,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
@@ -1299,7 +1299,7 @@
         <v>45968</v>
       </c>
       <c r="G20" s="9">
-        <v>4510</v>
+        <v>4063</v>
       </c>
       <c r="H20" s="3">
         <v>45931</v>
@@ -1319,7 +1319,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C21" s="9">
         <v>2025</v>
@@ -1334,16 +1334,16 @@
         <v>45968</v>
       </c>
       <c r="G21" s="9">
-        <v>4499</v>
+        <v>4865</v>
       </c>
       <c r="H21" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I21" s="2">
         <v>45964</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>14</v>
@@ -1354,7 +1354,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
@@ -1369,16 +1369,16 @@
         <v>45968</v>
       </c>
       <c r="G22" s="9">
-        <v>4445</v>
+        <v>4849</v>
       </c>
       <c r="H22" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I22" s="2">
         <v>45964</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>14</v>
@@ -1389,7 +1389,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
@@ -1404,16 +1404,16 @@
         <v>45968</v>
       </c>
       <c r="G23" s="9">
-        <v>4365</v>
+        <v>4848</v>
       </c>
       <c r="H23" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I23" s="2">
         <v>45964</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>14</v>
@@ -1424,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
@@ -1439,7 +1439,7 @@
         <v>45968</v>
       </c>
       <c r="G24" s="9">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="H24" s="3">
         <v>45931</v>
@@ -1448,7 +1448,7 @@
         <v>45964</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>14</v>
@@ -1459,7 +1459,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
@@ -1474,7 +1474,7 @@
         <v>45968</v>
       </c>
       <c r="G25" s="9">
-        <v>4326</v>
+        <v>4636</v>
       </c>
       <c r="H25" s="3">
         <v>45931</v>
@@ -1483,7 +1483,7 @@
         <v>45964</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>14</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
@@ -1509,7 +1509,7 @@
         <v>45968</v>
       </c>
       <c r="G26" s="9">
-        <v>4319</v>
+        <v>4578</v>
       </c>
       <c r="H26" s="3">
         <v>45931</v>
@@ -1529,7 +1529,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C27" s="9">
         <v>2025</v>
@@ -1544,7 +1544,7 @@
         <v>45968</v>
       </c>
       <c r="G27" s="9">
-        <v>4134</v>
+        <v>4510</v>
       </c>
       <c r="H27" s="3">
         <v>45931</v>
@@ -1564,7 +1564,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C28" s="9">
         <v>2025</v>
@@ -1579,7 +1579,7 @@
         <v>45968</v>
       </c>
       <c r="G28" s="9">
-        <v>4063</v>
+        <v>4499</v>
       </c>
       <c r="H28" s="3">
         <v>45931</v>
@@ -1588,7 +1588,7 @@
         <v>45964</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>14</v>
@@ -1634,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C30" s="9">
         <v>2025</v>
@@ -1649,10 +1649,10 @@
         <v>45968</v>
       </c>
       <c r="G30" s="9">
-        <v>3264</v>
+        <v>4527</v>
       </c>
       <c r="H30" s="3">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="I30" s="2">
         <v>45964</v>
@@ -1682,7 +1682,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K26" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K30">
       <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>
@@ -1750,7 +1750,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -1774,7 +1774,7 @@
         <v>45964</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>18</v>
@@ -1785,7 +1785,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -1809,7 +1809,7 @@
         <v>45964</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>18</v>
@@ -1820,7 +1820,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -1844,7 +1844,7 @@
         <v>45964</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>18</v>
@@ -1855,7 +1855,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -1890,7 +1890,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
